--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260814.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.05%</t>
+          <t>15.99%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.18%</t>
+          <t>6.33%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>79,000,000</t>
+          <t>1,690,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,635,000</t>
+          <t>79,000,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.32%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2,040,000</t>
+          <t>2,110,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>4.80%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.80%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -814,73 +814,73 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>214,500</t>
+          <t>610,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -902,139 +902,139 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4,250,000</t>
+          <t>214,500</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>4,250,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>2,190,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2,646,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,190,000</t>
+          <t>2,646,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,050,000</t>
+          <t>7,421,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1173,22 +1173,22 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>13,451,578,932</t>
+          <t>12,965,033,843</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>3,070,319,573</t>
+          <t>2,084,778,377</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
